--- a/diseases/d108/2010-2014.xlsx
+++ b/diseases/d108/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>9</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.167805553636668</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.3143092425775872</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.1227204171185164</v>
       </c>
@@ -2397,9 +2388,6 @@
       <c r="O11" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.07458024606074132</v>
       </c>
@@ -2941,9 +2929,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3485,9 +3470,6 @@
       <c r="O17" t="n">
         <v>4</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.07458024606074132</v>
       </c>
@@ -4029,9 +4011,6 @@
       <c r="O20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.04090680570617215</v>
       </c>
@@ -4573,9 +4552,6 @@
       <c r="O23" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.03729012303037066</v>
       </c>
@@ -5117,9 +5093,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -5661,9 +5634,6 @@
       <c r="O29" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.07458024606074132</v>
       </c>
@@ -6205,9 +6175,6 @@
       <c r="O32" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.06136020855925821</v>
       </c>
@@ -6749,9 +6716,6 @@
       <c r="O35" t="n">
         <v>6</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.111870369091112</v>
       </c>
@@ -7293,9 +7257,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7837,9 +7798,6 @@
       <c r="O41" t="n">
         <v>5</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.09322530757592666</v>
       </c>
@@ -8381,9 +8339,6 @@
       <c r="O44" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.04090680570617215</v>
       </c>
@@ -8925,9 +8880,6 @@
       <c r="O47" t="n">
         <v>10</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.1864506151518533</v>
       </c>
@@ -9469,9 +9421,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -10013,9 +9962,6 @@
       <c r="O53" t="n">
         <v>13</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.2423857996974093</v>
       </c>
@@ -10557,9 +10503,6 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -11101,9 +11044,6 @@
       <c r="O59" t="n">
         <v>7</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.1305154306062973</v>
       </c>
@@ -11645,9 +11585,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -12189,9 +12126,6 @@
       <c r="O65" t="n">
         <v>4</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.07458024606074132</v>
       </c>
@@ -12733,9 +12667,6 @@
       <c r="O68" t="n">
         <v>2</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.04090680570617215</v>
       </c>
@@ -13277,9 +13208,6 @@
       <c r="O71" t="n">
         <v>5</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.09322530757592666</v>
       </c>
@@ -13821,9 +13749,6 @@
       <c r="O74" t="n">
         <v>4</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.08181361141234429</v>
       </c>
@@ -14365,9 +14290,6 @@
       <c r="O77" t="n">
         <v>6</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.111353593872286</v>
       </c>
@@ -14909,9 +14831,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.3133450524382945</v>
       </c>
@@ -15305,9 +15224,6 @@
       <c r="O82" t="n">
         <v>3</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -15849,9 +15765,6 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -16393,9 +16306,6 @@
       <c r="O88" t="n">
         <v>3</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -16937,9 +16847,6 @@
       <c r="O91" t="n">
         <v>2</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.03711786462409532</v>
       </c>
@@ -17481,9 +17388,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -18025,9 +17929,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -18569,9 +18470,6 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -19113,9 +19011,6 @@
       <c r="O103" t="n">
         <v>5</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.0927946615602383</v>
       </c>
@@ -19657,9 +19552,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -20201,9 +20093,6 @@
       <c r="O109" t="n">
         <v>2</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.03711786462409532</v>
       </c>
@@ -20745,9 +20634,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -21289,9 +21175,6 @@
       <c r="O115" t="n">
         <v>7</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.1299125261843336</v>
       </c>
@@ -21833,9 +21716,6 @@
       <c r="O118" t="n">
         <v>3</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -22377,9 +22257,6 @@
       <c r="O121" t="n">
         <v>3</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.05567679693614298</v>
       </c>
@@ -22921,9 +22798,6 @@
       <c r="O124" t="n">
         <v>3</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -23465,9 +23339,6 @@
       <c r="O127" t="n">
         <v>4</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.07423572924819065</v>
       </c>
@@ -24009,9 +23880,6 @@
       <c r="O130" t="n">
         <v>2</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.04037982882182966</v>
       </c>
@@ -24553,9 +24421,6 @@
       <c r="O133" t="n">
         <v>3</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.05567679693614298</v>
       </c>
@@ -25097,9 +24962,6 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -25641,9 +25503,6 @@
       <c r="O139" t="n">
         <v>4</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.07423572924819065</v>
       </c>
@@ -26185,9 +26044,6 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -26729,9 +26585,6 @@
       <c r="O145" t="n">
         <v>6</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.111353593872286</v>
       </c>
@@ -27273,9 +27126,6 @@
       <c r="O148" t="n">
         <v>3</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -27817,9 +27667,6 @@
       <c r="O151" t="n">
         <v>2</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.03694145785584575</v>
       </c>
@@ -28361,9 +28208,6 @@
       <c r="O154" t="n">
         <v>4</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>1.246725397822283</v>
       </c>
@@ -28757,9 +28601,6 @@
       <c r="O156" t="n">
         <v>4</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.07970576616420483</v>
       </c>
@@ -29301,9 +29142,6 @@
       <c r="O159" t="n">
         <v>3</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.05541218678376863</v>
       </c>
@@ -29845,9 +29683,6 @@
       <c r="O162" t="n">
         <v>5</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.09963220770525605</v>
       </c>
@@ -30389,9 +30224,6 @@
       <c r="O165" t="n">
         <v>7</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.1292951024954601</v>
       </c>
@@ -30933,9 +30765,6 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -31477,9 +31306,6 @@
       <c r="O171" t="n">
         <v>3</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.05541218678376863</v>
       </c>
@@ -32021,9 +31847,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -32565,9 +32388,6 @@
       <c r="O177" t="n">
         <v>6</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.1108243735675373</v>
       </c>
@@ -33109,9 +32929,6 @@
       <c r="O180" t="n">
         <v>2</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.03985288308210241</v>
       </c>
@@ -33653,9 +33470,6 @@
       <c r="O183" t="n">
         <v>5</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.09235364463961437</v>
       </c>
@@ -34197,9 +34011,6 @@
       <c r="O186" t="n">
         <v>4</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.07970576616420483</v>
       </c>
@@ -34741,9 +34552,6 @@
       <c r="O189" t="n">
         <v>11</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.2031780182071516</v>
       </c>
@@ -35285,9 +35093,6 @@
       <c r="O192" t="n">
         <v>1</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -35829,9 +35634,6 @@
       <c r="O195" t="n">
         <v>6</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.1108243735675373</v>
       </c>
@@ -36373,9 +36175,6 @@
       <c r="O198" t="n">
         <v>2</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.03985288308210241</v>
       </c>
@@ -36917,9 +36716,6 @@
       <c r="O201" t="n">
         <v>7</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.1292951024954601</v>
       </c>
@@ -37461,9 +37257,6 @@
       <c r="O204" t="n">
         <v>4</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.07970576616420483</v>
       </c>
@@ -38005,9 +37798,6 @@
       <c r="O207" t="n">
         <v>5</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.09235364463961437</v>
       </c>
@@ -38549,9 +38339,6 @@
       <c r="O210" t="n">
         <v>1</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -39093,9 +38880,6 @@
       <c r="O213" t="n">
         <v>1</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -39637,9 +39421,6 @@
       <c r="O216" t="n">
         <v>3</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.05977932462315363</v>
       </c>
@@ -40181,9 +39962,6 @@
       <c r="O219" t="n">
         <v>7</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.1292951024954601</v>
       </c>
@@ -40725,9 +40503,6 @@
       <c r="O222" t="n">
         <v>3</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.05977932462315363</v>
       </c>
@@ -41417,9 +41192,6 @@
       <c r="O226" t="n">
         <v>7</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.1286988746018838</v>
       </c>
@@ -41961,9 +41733,6 @@
       <c r="O229" t="n">
         <v>1</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.3087510864178853</v>
       </c>
@@ -42357,9 +42126,6 @@
       <c r="O231" t="n">
         <v>4</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -42901,9 +42667,6 @@
       <c r="O234" t="n">
         <v>6</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.110313321087329</v>
       </c>
@@ -43445,9 +43208,6 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
@@ -43989,9 +43749,6 @@
       <c r="O240" t="n">
         <v>6</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.110313321087329</v>
       </c>
@@ -44533,9 +44290,6 @@
       <c r="O243" t="n">
         <v>1</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -45077,9 +44831,6 @@
       <c r="O246" t="n">
         <v>1</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -45621,9 +45372,6 @@
       <c r="O249" t="n">
         <v>1</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -46165,9 +45913,6 @@
       <c r="O252" t="n">
         <v>5</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.09192776757277416</v>
       </c>
@@ -46709,9 +46454,6 @@
       <c r="O255" t="n">
         <v>1</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -47253,9 +46995,6 @@
       <c r="O258" t="n">
         <v>10</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0.1838555351455483</v>
       </c>
@@ -47797,9 +47536,6 @@
       <c r="O261" t="n">
         <v>2</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.03936911388687422</v>
       </c>
@@ -48341,9 +48077,6 @@
       <c r="O264" t="n">
         <v>7</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.1286988746018838</v>
       </c>
@@ -48885,9 +48618,6 @@
       <c r="O267" t="n">
         <v>1</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -49429,9 +49159,6 @@
       <c r="O270" t="n">
         <v>4</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.07354221405821933</v>
       </c>
@@ -49973,9 +49700,6 @@
       <c r="O273" t="n">
         <v>1</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -50517,9 +50241,6 @@
       <c r="O276" t="n">
         <v>3</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.0551566605436645</v>
       </c>
@@ -51061,9 +50782,6 @@
       <c r="O279" t="n">
         <v>0</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0</v>
       </c>
@@ -51605,9 +51323,6 @@
       <c r="O282" t="n">
         <v>3</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.0551566605436645</v>
       </c>
@@ -52149,9 +51864,6 @@
       <c r="O285" t="n">
         <v>1</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -52693,9 +52405,6 @@
       <c r="O288" t="n">
         <v>4</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.07354221405821933</v>
       </c>
@@ -53237,9 +52946,6 @@
       <c r="O291" t="n">
         <v>4</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -53781,9 +53487,6 @@
       <c r="O294" t="n">
         <v>5</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.09192776757277416</v>
       </c>
@@ -54325,9 +54028,6 @@
       <c r="O297" t="n">
         <v>5</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0.09842278471718557</v>
       </c>
@@ -55017,9 +54717,6 @@
       <c r="O301" t="n">
         <v>6</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.1098562274932054</v>
       </c>
@@ -55561,9 +55258,6 @@
       <c r="O304" t="n">
         <v>4</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>1.221327430250754</v>
       </c>
@@ -55957,9 +55651,6 @@
       <c r="O306" t="n">
         <v>4</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.07786047208750739</v>
       </c>
@@ -56501,9 +56192,6 @@
       <c r="O309" t="n">
         <v>2</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.03661874249773513</v>
       </c>
@@ -57045,9 +56733,6 @@
       <c r="O312" t="n">
         <v>2</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0.0389302360437537</v>
       </c>
@@ -57589,9 +57274,6 @@
       <c r="O315" t="n">
         <v>7</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0.128165598742073</v>
       </c>
@@ -58133,9 +57815,6 @@
       <c r="O318" t="n">
         <v>2</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.0389302360437537</v>
       </c>
@@ -58677,9 +58356,6 @@
       <c r="O321" t="n">
         <v>5</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0.09154685624433782</v>
       </c>
@@ -59221,9 +58897,6 @@
       <c r="O324" t="n">
         <v>1</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -59765,9 +59438,6 @@
       <c r="O327" t="n">
         <v>2</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.03661874249773513</v>
       </c>
@@ -60309,9 +59979,6 @@
       <c r="O330" t="n">
         <v>2</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0.0389302360437537</v>
       </c>
@@ -60853,9 +60520,6 @@
       <c r="O333" t="n">
         <v>5</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0.09154685624433782</v>
       </c>
@@ -61397,9 +61061,6 @@
       <c r="O336" t="n">
         <v>4</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0.07786047208750739</v>
       </c>
@@ -61941,9 +61602,6 @@
       <c r="O339" t="n">
         <v>5</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0.09154685624433782</v>
       </c>
@@ -62485,9 +62143,6 @@
       <c r="O342" t="n">
         <v>1</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -63029,9 +62684,6 @@
       <c r="O345" t="n">
         <v>4</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0.07323748499547025</v>
       </c>
@@ -63573,9 +63225,6 @@
       <c r="O348" t="n">
         <v>1</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -64117,9 +63766,6 @@
       <c r="O351" t="n">
         <v>7</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0.128165598742073</v>
       </c>
@@ -64661,9 +64307,6 @@
       <c r="O354" t="n">
         <v>4</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0.07786047208750739</v>
       </c>
@@ -65205,9 +64848,6 @@
       <c r="O357" t="n">
         <v>11</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0.2014030837375432</v>
       </c>
@@ -65749,9 +65389,6 @@
       <c r="O360" t="n">
         <v>4</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0.07786047208750739</v>
       </c>
@@ -66293,9 +65930,6 @@
       <c r="O363" t="n">
         <v>6</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0.1098562274932054</v>
       </c>
@@ -66837,9 +66471,6 @@
       <c r="O366" t="n">
         <v>1</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -67381,9 +67012,6 @@
       <c r="O369" t="n">
         <v>5</v>
       </c>
-      <c r="Q369" t="n">
-        <v>0</v>
-      </c>
       <c r="R369" t="n">
         <v>0.09154685624433782</v>
       </c>
@@ -67924,9 +67552,6 @@
       </c>
       <c r="O372" t="n">
         <v>3</v>
-      </c>
-      <c r="Q372" t="n">
-        <v>0</v>
       </c>
       <c r="R372" t="n">
         <v>0.05839535406563053</v>
